--- a/.workspace/Certificacion_Quantify.xlsx
+++ b/.workspace/Certificacion_Quantify.xlsx
@@ -1233,7 +1233,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>

--- a/.workspace/Certificacion_Quantify.xlsx
+++ b/.workspace/Certificacion_Quantify.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Provider" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Reviewer" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Approver" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Admin" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Seguridad y Acceso" state="visible" r:id="rId8"/>
+    <sheet sheetId="2" name="Provider" state="visible" r:id="rId4"/>
+    <sheet sheetId="3" name="Reviewer" state="visible" r:id="rId5"/>
+    <sheet sheetId="4" name="Approver" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="Admin" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="Seguridad y Acceso" state="visible" r:id="rId8"/>
+    <sheet sheetId="1" name="Resumen" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="476">
   <si>
     <t>ID</t>
   </si>
@@ -71,7 +72,13 @@
     <t>Redirige al módulo Invoice. Menú lateral: Invoice, Help. Saludo "Hello, [nombre]" visible.</t>
   </si>
   <si>
-    <t/>
+    <t>Login correcto (email+password). Redirige a /invoice/invoices. Menú lateral real: "Bills" y "Help" (no dice literalmente "Invoice"). Saludo "Hello, Juan" visible. Aparece sección adicional "Administration &gt; Settings" no documentada.</t>
+  </si>
+  <si>
+    <t>⚠️ OK con diferencias de texto</t>
+  </si>
+  <si>
+    <t>Actualizar: el menú dice "Bills", no "Invoice". Agregar que existe módulo "Settings" bajo "Administration" para este rol.</t>
   </si>
   <si>
     <t>PRV-002</t>
@@ -92,6 +99,15 @@
     <t>Se muestra mensaje de error de credenciales inválidas. No se permite el acceso.</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>⏳ No verificado</t>
+  </si>
+  <si>
+    <t>No se probó en esta sesión de verificación en vivo.</t>
+  </si>
+  <si>
     <t>PRV-003</t>
   </si>
   <si>
@@ -112,6 +128,12 @@
     <t>Redirige al módulo Invoice post-autenticación SSO.</t>
   </si>
   <si>
+    <t>Botón "Microsoft" presente y funcional en pantalla de login (verificado visualmente).</t>
+  </si>
+  <si>
+    <t>Requiere cuenta Microsoft federada real para completar el flujo; no se ejecutó.</t>
+  </si>
+  <si>
     <t>PRV-004</t>
   </si>
   <si>
@@ -128,6 +150,15 @@
   </si>
   <si>
     <t>Se muestran solo facturas propias. Métricas: Pending Total, Overdue Amount, Payments this month. Columnas: Bill #, Provider, Company, Project, Deadline, Period, Amount, Action.</t>
+  </si>
+  <si>
+    <t>La lista carga con métricas Pending Total / Overdue Amount / Payments this month y filtros (Invoice Number, All companies, Advanced, Status, Period). Actualmente "No bills match your filters" (0 facturas cargadas).</t>
+  </si>
+  <si>
+    <t>🔴 Bloqueado (sin datos)</t>
+  </si>
+  <si>
+    <t>No hay facturas de prueba en el ambiente actual; no se puede confirmar que solo se vean facturas propias.</t>
   </si>
   <si>
     <t>PRV-005</t>
@@ -147,6 +178,12 @@
     <t>La tabla muestra solo facturas con el estado seleccionado.</t>
   </si>
   <si>
+    <t>Filtro "Status" presente ("0 selected").</t>
+  </si>
+  <si>
+    <t>No se puede validar el filtrado sin facturas de prueba.</t>
+  </si>
+  <si>
     <t>PRV-006</t>
   </si>
   <si>
@@ -163,6 +200,9 @@
     <t>La tabla muestra solo facturas del período seleccionado.</t>
   </si>
   <si>
+    <t>Filtro "Period" presente.</t>
+  </si>
+  <si>
     <t>PRV-007</t>
   </si>
   <si>
@@ -174,6 +214,12 @@
   </si>
   <si>
     <t>La tabla muestra la factura correspondiente al número ingresado.</t>
+  </si>
+  <si>
+    <t>Campo "Invoice Number" presente y coincide con lo documentado.</t>
+  </si>
+  <si>
+    <t>No hay facturas para validar la búsqueda.</t>
   </si>
   <si>
     <t>PRV-008</t>
@@ -200,6 +246,15 @@
     <t>La factura se crea en estado Draft. Aparece en la lista.</t>
   </si>
   <si>
+    <t>Formulario "Create Bill" carga (Year, Month, Company, Bill Number, líneas). El dropdown "Company" aparece deshabilitado con mensaje "Could not load dropdown options" (error 400 Bad Request en consola).</t>
+  </si>
+  <si>
+    <t>🔴 BUG confirmado</t>
+  </si>
+  <si>
+    <t>Bug bloqueante: no se puede seleccionar Company, por lo que no se puede completar ni guardar una factura nueva.</t>
+  </si>
+  <si>
     <t>PRV-009</t>
   </si>
   <si>
@@ -218,6 +273,15 @@
     <t>Ambas líneas se guardan. Total refleja la suma de todas las líneas.</t>
   </si>
   <si>
+    <t>No ejecutable: depende de poder seleccionar Company (ver PRV-008).</t>
+  </si>
+  <si>
+    <t>🔴 Bloqueado por bug</t>
+  </si>
+  <si>
+    <t>Mismo bug que PRV-008.</t>
+  </si>
+  <si>
     <t>PRV-010</t>
   </si>
   <si>
@@ -235,6 +299,9 @@
     <t>El documento queda adjunto a la factura.</t>
   </si>
   <si>
+    <t>Botón "Upload Document" y dropdown "Document Type" visibles, pero la fila completa depende del encabezado (Company) que está bloqueado.</t>
+  </si>
+  <si>
     <t>PRV-011</t>
   </si>
   <si>
@@ -249,6 +316,9 @@
     <t>El sistema muestra mensajes de validación. No permite enviar sin campos requeridos.</t>
   </si>
   <si>
+    <t>No se probó el envío del formulario vacío; además el bug de PRV-008 puede interferir.</t>
+  </si>
+  <si>
     <t>PRV-012</t>
   </si>
   <si>
@@ -263,6 +333,15 @@
     <t>Redirige a la lista sin crear ninguna factura.</t>
   </si>
   <si>
+    <t>Botón "Cancel" visible con enlace correcto a /invoice/invoices.</t>
+  </si>
+  <si>
+    <t>⏳ No verificado (elemento presente)</t>
+  </si>
+  <si>
+    <t>Se confirmó la presencia del botón, no se ejecutó el flujo completo.</t>
+  </si>
+  <si>
     <t>PRV-013</t>
   </si>
   <si>
@@ -283,6 +362,12 @@
     <t>La factura cambia de Draft a Submitted. Deja de ser editable.</t>
   </si>
   <si>
+    <t>No ejecutable actualmente: no existe forma de crear una factura en Draft por el bug de PRV-008.</t>
+  </si>
+  <si>
+    <t>Dependencia directa de PRV-008.</t>
+  </si>
+  <si>
     <t>PRV-014</t>
   </si>
   <si>
@@ -299,6 +384,9 @@
     <t>El sistema no permite editar facturas Submitted. Campos deshabilitados o sin opción de editar.</t>
   </si>
   <si>
+    <t>No hay facturas Submitted disponibles para probar.</t>
+  </si>
+  <si>
     <t>PRV-015</t>
   </si>
   <si>
@@ -311,6 +399,9 @@
     <t>Se muestra el detalle: número, período, company, project, líneas, documentos, estado.</t>
   </si>
   <si>
+    <t>No hay facturas cargadas para ver el detalle.</t>
+  </si>
+  <si>
     <t>PRV-016</t>
   </si>
   <si>
@@ -329,6 +420,15 @@
     <t>Pantalla Help con: Documentation, Live Chat, Email Support, FAQ, formulario "Send us a message".</t>
   </si>
   <si>
+    <t>La pantalla Help solo muestra el título "Help", sin Documentation, Live Chat, Email Support, FAQ ni formulario de contacto.</t>
+  </si>
+  <si>
+    <t>🔴 BUG / incompleto</t>
+  </si>
+  <si>
+    <t>El contenido descrito en el documento no existe actualmente en la pantalla real.</t>
+  </si>
+  <si>
     <t>PRV-017</t>
   </si>
   <si>
@@ -342,6 +442,12 @@
   </si>
   <si>
     <t>La pregunta se expande con su respuesta.</t>
+  </si>
+  <si>
+    <t>No aplica: no hay preguntas FAQ en la pantalla actual.</t>
+  </si>
+  <si>
+    <t>Depende de PRV-016.</t>
   </si>
   <si>
     <t>PRV-018</t>
@@ -358,6 +464,15 @@
   </si>
   <si>
     <t>Sesión cerrada. Redirige al login. Páginas protegidas inaccesibles sin re-autenticar.</t>
+  </si>
+  <si>
+    <t>Logout confirmado: menú de usuario (avatar "PU") → "Log out" → redirige al login de Keycloak.</t>
+  </si>
+  <si>
+    <t>✅ Verificado</t>
+  </si>
+  <si>
+    <t>Coincide con lo documentado.</t>
   </si>
   <si>
     <t>REV-001</t>
@@ -378,6 +493,15 @@
     <t>Redirige al Dashboard. Menú lateral: Dashboard, Invoice, Reports, Help.</t>
   </si>
   <si>
+    <t>Login correcto, redirige a /dashboard. Menú real: Dashboard, Bills, Help, Reports + sección "Administration &gt; Settings" (no documentada).</t>
+  </si>
+  <si>
+    <t>⚠️ OK con diferencias</t>
+  </si>
+  <si>
+    <t>Agregar módulo "Settings" al menú documentado para Reviewer.</t>
+  </si>
+  <si>
     <t>REV-002</t>
   </si>
   <si>
@@ -396,6 +520,15 @@
     <t>4 tarjetas de métricas + gráficas Bills Trend, Bills by Status, Top Providers by Volume + sección Recent Bills.</t>
   </si>
   <si>
+    <t>4 tarjetas de métricas + Bills Trend + Bills by Status + Top Providers by Volume + Recent Bills presentes. Con la BD vacía se muestra "No data to display."</t>
+  </si>
+  <si>
+    <t>✅ Verificado (estructura)</t>
+  </si>
+  <si>
+    <t>Estructura coincide; contenido vacío por falta de datos.</t>
+  </si>
+  <si>
     <t>REV-003</t>
   </si>
   <si>
@@ -408,6 +541,9 @@
     <t>Redirige a la lista de Invoice.</t>
   </si>
   <si>
+    <t>Botón "View Bills" presente con enlace a /invoice/invoices.</t>
+  </si>
+  <si>
     <t>REV-004</t>
   </si>
   <si>
@@ -421,6 +557,15 @@
   </si>
   <si>
     <t>Lista con facturas de todos los proveedores. Por defecto filtrado para Submitted/Draft. Sin botón "Create Bill".</t>
+  </si>
+  <si>
+    <t>BUG CRÍTICO: al entrar a Bills como Reviewer, la pantalla mostró datos de sesión del Provider ("Hello, Juan" + botón "Create Bill", que el Reviewer no debería tener). Consola: "Hydration completed but contains mismatches."</t>
+  </si>
+  <si>
+    <t>🔴 BUG CRÍTICO confirmado</t>
+  </si>
+  <si>
+    <t>Posible filtrado/caché de SSR entre usuarios: riesgo de fuga de datos entre sesiones/roles. Reportar como bug de prioridad alta y volver a verificar con refresco forzado.</t>
   </si>
   <si>
     <t>REV-005</t>
@@ -434,6 +579,12 @@
   </si>
   <si>
     <t>Solo se muestran facturas Submitted.</t>
+  </si>
+  <si>
+    <t>No verificable de forma confiable por el bug de REV-004.</t>
+  </si>
+  <si>
+    <t>Repetir la prueba una vez corregido el bug de hidratación.</t>
   </si>
   <si>
     <t>REV-006</t>
@@ -455,6 +606,12 @@
   </si>
   <si>
     <t>Factura cambia a estado Reviewed.</t>
+  </si>
+  <si>
+    <t>🔴 Bloqueado (sin datos + bug)</t>
+  </si>
+  <si>
+    <t>No hay facturas Submitted disponibles y persiste el riesgo del bug de REV-004.</t>
   </si>
   <si>
     <t>REV-007</t>
@@ -473,6 +630,9 @@
     <t>Factura cambia a estado Rejected.</t>
   </si>
   <si>
+    <t>Igual a REV-006.</t>
+  </si>
+  <si>
     <t>REV-008</t>
   </si>
   <si>
@@ -485,6 +645,9 @@
     <t>Detalle completo: encabezado, líneas, documentos, historial de estados.</t>
   </si>
   <si>
+    <t>No hay facturas para ver detalle.</t>
+  </si>
+  <si>
     <t>REV-009</t>
   </si>
   <si>
@@ -498,6 +661,9 @@
   </si>
   <si>
     <t>Página Reports: sección FILTERS (Status, Provider, Period) + 4 métricas (Gross Amount, IRS Withholding, ITBS Withholding, Net Payable) + gráficas + tabla Detail.</t>
+  </si>
+  <si>
+    <t>No se navegó a Reports en esta sesión.</t>
   </si>
   <si>
     <t>REV-010</t>
@@ -564,6 +730,12 @@
     <t>Pantalla Help completa con FAQ, soporte, formulario de contacto.</t>
   </si>
   <si>
+    <t>La pantalla Help solo muestra el título "Help", sin contenido adicional.</t>
+  </si>
+  <si>
+    <t>Mismo hallazgo que PRV-016 (pantalla compartida entre roles).</t>
+  </si>
+  <si>
     <t>REV-015</t>
   </si>
   <si>
@@ -572,6 +744,9 @@
   </si>
   <si>
     <t>Sesión cerrada. Redirige al login de Keycloak.</t>
+  </si>
+  <si>
+    <t>Logout confirmado: menú de usuario (avatar "RU") → "Log out" → redirige al login.</t>
   </si>
   <si>
     <t>APP-001</t>
@@ -592,6 +767,12 @@
     <t>Redirige al Dashboard. Menú lateral: Dashboard, Invoice, Help.</t>
   </si>
   <si>
+    <t>Login correcto, redirige a /dashboard. Menú real: Dashboard, Bills, Help + "Administration &gt; Settings" (sin Reports, correcto).</t>
+  </si>
+  <si>
+    <t>Agregar módulo "Settings" al menú documentado para Approver.</t>
+  </si>
+  <si>
     <t>APP-002</t>
   </si>
   <si>
@@ -601,6 +782,9 @@
     <t>4 tarjetas de métricas + gráficas Bills Trend, Bills by Status, Top Providers + Recent Bills.</t>
   </si>
   <si>
+    <t>Verificado con datos reales: tarjetas de métricas (Rejected $10,980 / 4 bills, Total Volume $37,990 / 16 bills), gráficas y Recent Bills con datos reales.</t>
+  </si>
+  <si>
     <t>APP-003</t>
   </si>
   <si>
@@ -611,6 +795,9 @@
   </si>
   <si>
     <t>Facturas en estado Reviewed por defecto (filtro "1 selected"). Sin botón "Create Bill".</t>
+  </si>
+  <si>
+    <t>No se navegó a Bills como Approver en esta sesión.</t>
   </si>
   <si>
     <t>APP-004</t>
@@ -679,10 +866,22 @@
     <t>No existe botón Create Bill. Acceso directo muestra error de permisos.</t>
   </si>
   <si>
+    <t>No se confirmó la ausencia del botón "Create Bill" para Approver en esta sesión.</t>
+  </si>
+  <si>
     <t>APP-009</t>
   </si>
   <si>
+    <t>La pantalla Help solo muestra el título "Help", sin contenido adicional (mismo componente compartido verificado para Provider/Reviewer).</t>
+  </si>
+  <si>
+    <t>Extrapolado del mismo hallazgo en otros roles (ruta /help compartida).</t>
+  </si>
+  <si>
     <t>APP-010</t>
+  </si>
+  <si>
+    <t>Logout confirmado: menú de usuario (avatar "AU") → "Log out" → redirige al login.</t>
   </si>
   <si>
     <t>ADM-001</t>
@@ -703,6 +902,15 @@
     <t>Redirige al Dashboard. Menú lateral: Dashboard, Providers, Invoice, Users, Reports, Quickbook, Help.</t>
   </si>
   <si>
+    <t>Login correcto, redirige a /dashboard. Menú real: Dashboard, Providers, Bills, Companies, Help + "Administration &gt; Users, Reports, Settings".</t>
+  </si>
+  <si>
+    <t>⚠️ Desactualizado</t>
+  </si>
+  <si>
+    <t>Diferencias: aparece módulo nuevo "Companies" (no documentado); NO existe un ítem de menú "Quickbook" (ver ADM-021/022); aparece "Settings" nuevo.</t>
+  </si>
+  <si>
     <t>ADM-002</t>
   </si>
   <si>
@@ -712,6 +920,9 @@
     <t>4 tarjetas de métricas + gráficas Bills Trend, Bills by Status, Top Providers by Volume + Recent Bills.</t>
   </si>
   <si>
+    <t>Verificado con datos reales: métricas, Bills Trend, Bills by Status, Top Providers, Recent Bills con datos reales.</t>
+  </si>
+  <si>
     <t>ADM-003</t>
   </si>
   <si>
@@ -734,6 +945,12 @@
   </si>
   <si>
     <t>Lista con columnas: estado (badge), Provider Type, Provider Name, Vendor ID, Action. Filtros: Provider Type, Status, Provider.</t>
+  </si>
+  <si>
+    <t>Lista carga con filtros Provider Type (All/Contractor/Vendor), Status y buscador "Search by name...". Botón real es "Create Provider" (sin "+"). Actualmente 0 proveedores.</t>
+  </si>
+  <si>
+    <t>El filtro Status tiene más opciones que las documentadas: All, Active, Completed, Pending Confirmation, Disabled, Cancelled, Draft (se agregaron "Completed" y "Pending Confirmation").</t>
   </si>
   <si>
     <t>ADM-005</t>
@@ -754,6 +971,9 @@
     <t>Proveedor creado en estado Draft. Visible en la lista.</t>
   </si>
   <si>
+    <t>No se completó el formulario de creación en esta sesión.</t>
+  </si>
+  <si>
     <t>ADM-006</t>
   </si>
   <si>
@@ -826,6 +1046,9 @@
     <t>El estado del proveedor se actualiza al nuevo estado.</t>
   </si>
   <si>
+    <t>No hay proveedores de prueba para ejecutar la acción.</t>
+  </si>
+  <si>
     <t>ADM-011</t>
   </si>
   <si>
@@ -836,6 +1059,9 @@
   </si>
   <si>
     <t>Lista con facturas de TODOS los proveedores. Columnas: estado, Bill #, Provider, Company, Project, Deadline, Period, Amount, Action.</t>
+  </si>
+  <si>
+    <t>No se abrió Bills como Admin en esta sesión. Se detectó un bug de hidratación/caché al ver Bills como Reviewer (REV-004); recomendable re-verificar también con Admin.</t>
   </si>
   <si>
     <t>ADM-012</t>
@@ -877,6 +1103,12 @@
   </si>
   <si>
     <t>"Users &amp; Roles": tarjetas de conteo (Admins, Reviewers, Approvers, Providers), buscador, filtro All Roles, tabla: USER, EMAIL, ROLE, COMPANY, STATUS.</t>
+  </si>
+  <si>
+    <t>Página "Users" carga con filtros Role (All/Admin/Reviewer/Approver/Provider) y Status (All/Active/Disabled) + buscador "Search by name or email...". El botón real es "Invite User", no "+ Add User". No se observaron las tarjetas de conteo por rol (Admins/Reviewers/Approvers/Providers); el encabezado solo muestra "X users". Actualmente 0 usuarios.</t>
+  </si>
+  <si>
+    <t>Actualizar: el botón se llama "Invite User" (sugiere flujo de invitación por email, no creación directa). Confirmar si las tarjetas de conteo por rol siguen existiendo en la UI real.</t>
   </si>
   <si>
     <t>ADM-015</t>
@@ -899,6 +1131,9 @@
     <t>Usuario creado y visible en la tabla.</t>
   </si>
   <si>
+    <t>El botón ahora es "Invite User"; el flujo podría ser distinto al de "+ Add User" documentado (posible invitación por correo en vez de alta directa). Verificar antes de re-certificar.</t>
+  </si>
+  <si>
     <t>ADM-016</t>
   </si>
   <si>
@@ -945,6 +1180,9 @@
     <t>Página Reports con sección FILTERS, métricas y tabla Detail.</t>
   </si>
   <si>
+    <t>Enlace "Reports" presente en el menú; no se exploró la pantalla.</t>
+  </si>
+  <si>
     <t>ADM-020</t>
   </si>
   <si>
@@ -976,6 +1214,15 @@
     <t>Estado de conexión (Connected/Disconnected), Realm ID, Environment, fecha conexión, sección de sincronización.</t>
   </si>
   <si>
+    <t>NO existe un ítem de menú "Quickbook". En su lugar aparece un badge "QuickBooks Not Connected" en la barra lateral, y en Settings &gt; "Accounting Accounts" se menciona "Expense and COGS accounts synced from QuickBooks Online."</t>
+  </si>
+  <si>
+    <t>🔴 Desactualizado (flujo cambió)</t>
+  </si>
+  <si>
+    <t>Reescribir el caso de prueba: la conexión/estado de QuickBooks ya no tiene pantalla propia; ahora vive como badge + sección dentro de Settings. Falta documentar el flujo real completo.</t>
+  </si>
+  <si>
     <t>ADM-022</t>
   </si>
   <si>
@@ -992,10 +1239,22 @@
     <t>Sincronización ejecutada. Resultado muestra: Fetched, Created, Updated y fecha/hora del sync.</t>
   </si>
   <si>
+    <t>No se encontró una pantalla dedicada de sincronización de Vendors con botón "Sync" como se describe.</t>
+  </si>
+  <si>
+    <t>Mismo hallazgo que ADM-021. Requiere levantamiento de UI-UX actualizado antes de redactar steps nuevos.</t>
+  </si>
+  <si>
     <t>ADM-023</t>
   </si>
   <si>
     <t>Pantalla Help completa.</t>
+  </si>
+  <si>
+    <t>La pantalla Help solo muestra el título "Help", sin contenido adicional (mismo hallazgo que otros roles).</t>
+  </si>
+  <si>
+    <t>Ruta /help compartida entre todos los roles.</t>
   </si>
   <si>
     <t>ADM-024</t>
@@ -1005,6 +1264,15 @@
 2. Clic en "Log out"</t>
   </si>
   <si>
+    <t>No se ejecutó el logout explícito para Admin en esta sesión, pero el mismo patrón de menú de usuario → "Log out" se confirmó 3 veces (Provider, Reviewer, Approver).</t>
+  </si>
+  <si>
+    <t>⚠️ Muy probable OK (no ejecutado)</t>
+  </si>
+  <si>
+    <t>Confirmar en próxima sesión por consistencia con los otros 3 roles.</t>
+  </si>
+  <si>
     <t>SEC-001</t>
   </si>
   <si>
@@ -1018,6 +1286,9 @@
   </si>
   <si>
     <t>Sin acceso al Dashboard. Redirige a Invoice o muestra error de permisos.</t>
+  </si>
+  <si>
+    <t>No se intentó acceso directo a /dashboard como Provider en esta sesión.</t>
   </si>
   <si>
     <t>SEC-002</t>
@@ -1057,6 +1328,15 @@
     <t>Solo aparecen facturas del provider autenticado.</t>
   </si>
   <si>
+    <t>Hallazgo relacionado: se detectó que Reviewer, al entrar a Bills, mostró momentáneamente datos/sesión de Provider (bug de hidratación, ver REV-004). Esto es un riesgo de aislamiento de datos entre sesiones, aunque no es exactamente este escenario (Provider viendo facturas ajenas).</t>
+  </si>
+  <si>
+    <t>⚠️ Riesgo relacionado detectado</t>
+  </si>
+  <si>
+    <t>Priorizar la investigación del bug de REV-004 antes de certificar este módulo de seguridad.</t>
+  </si>
+  <si>
     <t>SEC-005</t>
   </si>
   <si>
@@ -1136,13 +1416,136 @@
   <si>
     <t xml:space="preserve">1. Verificar que no existe botón "Create Bill" para Admin
 2. Intentar navegar a /invoice/new-invoice</t>
+  </si>
+  <si>
+    <t>Rol</t>
+  </si>
+  <si>
+    <t>Estado del módulo</t>
+  </si>
+  <si>
+    <t>Detalle</t>
+  </si>
+  <si>
+    <t>Provider</t>
+  </si>
+  <si>
+    <t>✅ Completo</t>
+  </si>
+  <si>
+    <t>Login, credenciales incorrectas (no probado) y SSO (no probado) — el login base funciona.</t>
+  </si>
+  <si>
+    <t>Bill — Lista</t>
+  </si>
+  <si>
+    <t>🔴 Bloqueado</t>
+  </si>
+  <si>
+    <t>UI correcta pero sin datos de prueba (facturas) para validar filtros/búsqueda/detalle.</t>
+  </si>
+  <si>
+    <t>🔴 Bloqueado (BUG)</t>
+  </si>
+  <si>
+    <t>Dropdown "Company" no carga (400 Bad Request). No se puede crear ninguna factura.</t>
+  </si>
+  <si>
+    <t>Depende de Create Bill (bug) y de datos existentes.</t>
+  </si>
+  <si>
+    <t>🔴 Incompleto</t>
+  </si>
+  <si>
+    <t>Pantalla vacía: solo título "Help", sin FAQ/soporte/formulario.</t>
+  </si>
+  <si>
+    <t>Verificado end-to-end.</t>
+  </si>
+  <si>
+    <t>Reviewer</t>
+  </si>
+  <si>
+    <t>⚠️ Completo con ajuste de texto</t>
+  </si>
+  <si>
+    <t>Funciona; el menú dice "Bills" no "Invoice"; agregar "Settings" al documento.</t>
+  </si>
+  <si>
+    <t>Estructura verificada (tarjetas, gráficas, Recent Bills, botón View Bills).</t>
+  </si>
+  <si>
+    <t>Bill — Lista/Acción</t>
+  </si>
+  <si>
+    <t>🔴 Bloqueado (BUG CRÍTICO)</t>
+  </si>
+  <si>
+    <t>Se detectaron datos de otra sesión (Provider) al cargar Bills como Reviewer + "Hydration mismatch". Prioridad alta.</t>
+  </si>
+  <si>
+    <t>No explorado en esta sesión.</t>
+  </si>
+  <si>
+    <t>Mismo hallazgo que Provider.</t>
+  </si>
+  <si>
+    <t>Approver</t>
+  </si>
+  <si>
+    <t>Funciona; agregar "Settings" al documento; sin Reports (correcto).</t>
+  </si>
+  <si>
+    <t>Verificado con datos reales (montos, gráficas, Recent Bills).</t>
+  </si>
+  <si>
+    <t>Extrapolado del mismo hallazgo compartido.</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Aparece módulo nuevo "Companies"; NO existe ítem de menú "Quickbook"; aparece "Settings".</t>
+  </si>
+  <si>
+    <t>Verificado con datos reales.</t>
+  </si>
+  <si>
+    <t>⚠️ Completo con ajustes</t>
+  </si>
+  <si>
+    <t>Botón real "Create Provider" (sin "+"); Status tiene 2 opciones nuevas (Completed, Pending Confirmation); 0 proveedores cargados.</t>
+  </si>
+  <si>
+    <t>Botón real "Invite User" (no "+ Add User"); no se vieron tarjetas de conteo por rol; 0 usuarios cargados.</t>
+  </si>
+  <si>
+    <t>No existe pantalla "Quickbook" dedicada; ahora es un badge + sección en Settings &gt; Accounting Accounts. Reescribir TCs.</t>
+  </si>
+  <si>
+    <t>Mismo hallazgo compartido.</t>
+  </si>
+  <si>
+    <t>⚠️ Muy probable OK</t>
+  </si>
+  <si>
+    <t>No ejecutado para Admin, pero confirmado 3/4 roles con el mismo patrón.</t>
+  </si>
+  <si>
+    <t>Todos</t>
+  </si>
+  <si>
+    <t>Seguridad y Acceso</t>
+  </si>
+  <si>
+    <t>No se probó ningún escenario de acceso restringido en esta sesión. Se detectó un riesgo relacionado en Reviewer (ver Bill — Lista/Acción).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1163,14 +1566,16 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
+      <color rgb="FF006100"/>
     </font>
     <font>
       <b/>
       <color rgb="FF9C0006"/>
       <sz val="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF404040"/>
     </font>
     <font>
       <b/>
@@ -1203,13 +1608,23 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF8B0000"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <color rgb="FF9C0006"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1228,6 +1643,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFD7D7"/>
       </patternFill>
     </fill>
@@ -1238,12 +1658,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -1284,6 +1704,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFAD7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1329,7 +1759,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1337,90 +1767,77 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1760,6 +2177,401 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>435</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>436</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>439</v>
+      </c>
+      <c r="D2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>442</v>
+      </c>
+      <c r="D3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="D4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>442</v>
+      </c>
+      <c r="D5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>438</v>
+      </c>
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="D6" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>438</v>
+      </c>
+      <c r="B7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>439</v>
+      </c>
+      <c r="D7" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>450</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="D8" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>450</v>
+      </c>
+      <c r="B9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>439</v>
+      </c>
+      <c r="D9" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>450</v>
+      </c>
+      <c r="B10" t="s">
+        <v>454</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>455</v>
+      </c>
+      <c r="D10" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>450</v>
+      </c>
+      <c r="B11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>450</v>
+      </c>
+      <c r="B12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="D12" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>450</v>
+      </c>
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>439</v>
+      </c>
+      <c r="D13" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>459</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="D14" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>459</v>
+      </c>
+      <c r="B15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>439</v>
+      </c>
+      <c r="D15" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>459</v>
+      </c>
+      <c r="B16" t="s">
+        <v>454</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>459</v>
+      </c>
+      <c r="B17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="D17" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>459</v>
+      </c>
+      <c r="B18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>439</v>
+      </c>
+      <c r="D18" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>463</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="D19" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>463</v>
+      </c>
+      <c r="B20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>439</v>
+      </c>
+      <c r="D20" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>463</v>
+      </c>
+      <c r="B21" t="s">
+        <v>284</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>466</v>
+      </c>
+      <c r="D21" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>463</v>
+      </c>
+      <c r="B22" t="s">
+        <v>332</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="D22" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>463</v>
+      </c>
+      <c r="B23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>463</v>
+      </c>
+      <c r="B24" t="s">
+        <v>366</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="D24" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>463</v>
+      </c>
+      <c r="B25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="D25" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>463</v>
+      </c>
+      <c r="B26" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>471</v>
+      </c>
+      <c r="D26" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>473</v>
+      </c>
+      <c r="B27" t="s">
+        <v>474</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" t="s">
+        <v>475</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF1D6FA4"/>
   </sheetPr>
@@ -1836,564 +2648,564 @@
         <v>17</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="J4" s="8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="E6" s="8" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="E7" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="J7" s="8" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>25</v>
-      </c>
       <c r="E8" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>17</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF217346"/>
@@ -2447,492 +3259,492 @@
     </row>
     <row r="2" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>103</v>
+      <c r="C2" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>17</v>
+      <c r="E2" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>109</v>
+        <v>148</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>17</v>
+      <c r="E3" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="4" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>113</v>
+      <c r="A4" s="13" t="s">
+        <v>157</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>118</v>
+        <v>162</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>17</v>
+      <c r="E5" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>122</v>
+      <c r="A6" s="13" t="s">
+        <v>170</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>124</v>
+        <v>172</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>17</v>
+        <v>174</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>17</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>128</v>
+        <v>176</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>17</v>
+      <c r="E7" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>132</v>
+      <c r="A8" s="13" t="s">
+        <v>184</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>17</v>
+        <v>182</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>136</v>
+      <c r="A9" s="13" t="s">
+        <v>189</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>138</v>
+        <v>191</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>17</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>142</v>
+        <v>194</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>17</v>
+      <c r="E10" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>145</v>
+      <c r="A11" s="13" t="s">
+        <v>200</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>146</v>
+        <v>201</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>147</v>
+        <v>202</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>149</v>
+        <v>204</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
-        <v>150</v>
+      <c r="A12" s="13" t="s">
+        <v>205</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>147</v>
+        <v>202</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>152</v>
+        <v>207</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>153</v>
+        <v>208</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>154</v>
+      <c r="A13" s="13" t="s">
+        <v>209</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>147</v>
+        <v>202</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>156</v>
+        <v>211</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>157</v>
+        <v>212</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>158</v>
+      <c r="A14" s="13" t="s">
+        <v>213</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>159</v>
+        <v>214</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>88</v>
+        <v>218</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>17</v>
+        <v>119</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="16" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>99</v>
+        <v>223</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>17</v>
+      <c r="E16" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF7B3F9E"/>
@@ -2953,365 +3765,365 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="A2" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>170</v>
+      <c r="C2" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>17</v>
+      <c r="E2" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>109</v>
+      <c r="A3" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>17</v>
+      <c r="E3" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>178</v>
+      <c r="A4" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>239</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>17</v>
+      <c r="E4" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="5" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>182</v>
+      <c r="A5" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>244</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="G5" s="19" t="s">
+      <c r="E5" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>185</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>133</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>135</v>
-      </c>
       <c r="H6" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>189</v>
+      <c r="A7" s="16" t="s">
+        <v>251</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>190</v>
+        <v>252</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>138</v>
+        <v>191</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B8" s="18" t="s">
+      <c r="A8" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>17</v>
+      <c r="E8" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>196</v>
+      <c r="A9" s="16" t="s">
+        <v>258</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>197</v>
+        <v>259</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>199</v>
+        <v>261</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>17</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>88</v>
+      <c r="A10" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>17</v>
+        <v>119</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>99</v>
+      <c r="A11" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>17</v>
+      <c r="E11" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFB8500A"/>
@@ -3332,813 +4144,813 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" s="23" t="s">
+      <c r="A2" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>203</v>
+      <c r="C2" s="19" t="s">
+        <v>269</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>17</v>
+      <c r="E2" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>109</v>
+      <c r="A3" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>150</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="24" t="s">
-        <v>17</v>
+      <c r="E3" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>210</v>
+      <c r="A4" s="21" t="s">
+        <v>280</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>211</v>
+        <v>281</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>215</v>
+      <c r="A5" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>285</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>17</v>
+      <c r="E5" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>218</v>
+      <c r="A6" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>214</v>
+        <v>284</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>219</v>
+        <v>291</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>220</v>
+        <v>292</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>221</v>
+        <v>293</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>17</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
-        <v>222</v>
+      <c r="A7" s="21" t="s">
+        <v>295</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>214</v>
+        <v>284</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>223</v>
+        <v>296</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>224</v>
+        <v>297</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>225</v>
+        <v>298</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
-        <v>226</v>
+      <c r="A8" s="21" t="s">
+        <v>299</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>214</v>
+        <v>284</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>227</v>
+        <v>300</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>228</v>
+        <v>301</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>229</v>
+        <v>302</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
-        <v>231</v>
+      <c r="A9" s="21" t="s">
+        <v>304</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>214</v>
+        <v>284</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>232</v>
+        <v>305</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>233</v>
+        <v>306</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>234</v>
+        <v>307</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
-        <v>235</v>
+      <c r="A10" s="21" t="s">
+        <v>308</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>214</v>
+        <v>284</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>236</v>
+        <v>309</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>237</v>
+        <v>310</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>238</v>
+        <v>311</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>239</v>
+      <c r="A11" s="21" t="s">
+        <v>312</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>214</v>
+        <v>284</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>240</v>
+        <v>313</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>241</v>
+        <v>314</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>242</v>
+        <v>315</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>243</v>
+        <v>316</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>17</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>118</v>
+      <c r="A12" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>163</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>17</v>
+      <c r="E12" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="25" t="s">
-        <v>248</v>
+      <c r="A13" s="21" t="s">
+        <v>323</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>245</v>
+        <v>319</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>249</v>
+        <v>324</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
-        <v>252</v>
+      <c r="A14" s="21" t="s">
+        <v>327</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>245</v>
+        <v>319</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>253</v>
+        <v>328</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>254</v>
+        <v>329</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>255</v>
+        <v>330</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>258</v>
+      <c r="A15" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>333</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>17</v>
+      <c r="E15" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="16" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
-        <v>261</v>
+      <c r="A16" s="21" t="s">
+        <v>338</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>262</v>
+        <v>339</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>263</v>
+        <v>340</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>264</v>
+        <v>341</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>265</v>
+        <v>342</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>17</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>266</v>
+      <c r="A17" s="21" t="s">
+        <v>344</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>267</v>
+        <v>345</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>268</v>
+        <v>346</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>269</v>
+        <v>347</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>270</v>
+        <v>348</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
-        <v>271</v>
+      <c r="A18" s="21" t="s">
+        <v>349</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>272</v>
+        <v>350</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>263</v>
+        <v>340</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>273</v>
+        <v>351</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>274</v>
+        <v>352</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>275</v>
+      <c r="A19" s="21" t="s">
+        <v>353</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>276</v>
+        <v>354</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>263</v>
+        <v>340</v>
       </c>
       <c r="F19" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="G20" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="H20" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="24" t="s">
-        <v>17</v>
+      <c r="F20" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="21" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
-        <v>281</v>
+      <c r="A21" s="21" t="s">
+        <v>360</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>282</v>
+        <v>361</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>283</v>
+        <v>362</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>284</v>
+        <v>363</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>285</v>
+        <v>364</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>288</v>
+      <c r="A22" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>367</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="G22" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="23" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
-        <v>291</v>
+      <c r="A23" s="21" t="s">
+        <v>373</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>287</v>
+        <v>366</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>292</v>
+        <v>374</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>293</v>
+        <v>375</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>294</v>
+        <v>376</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>295</v>
+        <v>377</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>17</v>
+        <v>378</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>17</v>
+        <v>371</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>17</v>
+        <v>379</v>
       </c>
     </row>
     <row r="24" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
-        <v>296</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>88</v>
+      <c r="A24" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>118</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="H24" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="24" t="s">
-        <v>17</v>
+        <v>119</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="25" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>99</v>
+      <c r="A25" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>134</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I25" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="24" t="s">
-        <v>17</v>
+      <c r="E25" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J25"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF8B0000"/>
@@ -4159,392 +4971,392 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="22" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>302</v>
+      <c r="A2" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>391</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="29" t="s">
-        <v>303</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>304</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>17</v>
+      <c r="E2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
-        <v>305</v>
+      <c r="A3" s="24" t="s">
+        <v>395</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>306</v>
+        <v>396</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>307</v>
+        <v>397</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>308</v>
+        <v>398</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
-        <v>309</v>
+      <c r="A4" s="24" t="s">
+        <v>399</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>310</v>
+        <v>400</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>311</v>
+        <v>401</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>308</v>
+        <v>398</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
-        <v>312</v>
+      <c r="A5" s="24" t="s">
+        <v>402</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>313</v>
+        <v>403</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>314</v>
+        <v>404</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>315</v>
+        <v>405</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>316</v>
+        <v>406</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>17</v>
+        <v>407</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>17</v>
+        <v>408</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>17</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
-        <v>317</v>
+      <c r="A6" s="24" t="s">
+        <v>410</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>318</v>
+        <v>411</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>319</v>
+        <v>412</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>320</v>
+        <v>413</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
-        <v>321</v>
+      <c r="A7" s="24" t="s">
+        <v>414</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>322</v>
+        <v>415</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>323</v>
+        <v>416</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
-        <v>325</v>
+      <c r="A8" s="24" t="s">
+        <v>418</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>197</v>
+        <v>259</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>319</v>
+        <v>412</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>320</v>
+        <v>413</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
-        <v>326</v>
+      <c r="A9" s="24" t="s">
+        <v>419</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>328</v>
+        <v>421</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>329</v>
+        <v>422</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
-        <v>330</v>
+      <c r="A10" s="24" t="s">
+        <v>423</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>331</v>
+        <v>424</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>332</v>
+        <v>425</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>333</v>
+        <v>426</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
-        <v>334</v>
+      <c r="A11" s="24" t="s">
+        <v>427</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>335</v>
+        <v>428</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>336</v>
+        <v>429</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>337</v>
+        <v>430</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>338</v>
+        <v>431</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
-        <v>339</v>
+      <c r="A12" s="24" t="s">
+        <v>432</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>340</v>
+        <v>433</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>320</v>
+        <v>413</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>